--- a/Assets/Excels/SpawnLaneData.xlsx
+++ b/Assets/Excels/SpawnLaneData.xlsx
@@ -1,69 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\valha\OneDrive\문서\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94F2078-E9DE-40C7-A6E2-2955FEBE8F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild="10.105.262.54977"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11925" windowHeight="15600" xr2:uid="{8F59915E-3DCF-470C-BE8A-F0D389DEE6E6}"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="SpawnLaneData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Pattern_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>lanes</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"single_1"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"single_2"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"single_3"</t>
@@ -76,7 +48,6 @@
   </si>
   <si>
     <t>"1"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"2"</t>
@@ -92,19 +63,15 @@
   </si>
   <si>
     <t>"1,2"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"double_1,2"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"double_1,3"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"1,3"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"double_1,4"</t>
@@ -120,7 +87,6 @@
   </si>
   <si>
     <t>"double_2,3"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"double_2,4"</t>
@@ -130,7 +96,6 @@
   </si>
   <si>
     <t>"2,3"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"2,4"</t>
@@ -140,56 +105,45 @@
   </si>
   <si>
     <t>"double_3,4"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"3,4"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"double_4,5"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"4,5"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"triple_1,2,3"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"1,2,3"</t>
   </si>
   <si>
     <t>"1,2,3"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"triple_1,2,4"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"1,2,4"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"triple_1,2,5"</t>
   </si>
   <si>
     <t>"1,2,5"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"triple_2,3,4"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"2,3,4"</t>
   </si>
   <si>
     <t>"2,3,4"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"triple_2,3,5"</t>
@@ -199,65 +153,51 @@
   </si>
   <si>
     <t>"triple_3,4,5"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"3,4,5"</t>
   </si>
   <si>
     <t>"3,4,5"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"quadra_1,2,3,4"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"1,2,3,4"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"quadra_1,2,3,5"</t>
   </si>
   <si>
     <t>"1,2,3,5"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"quadra_2,3,4,5"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"2,3,4,5"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"quadra_1,3,4,5"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"1,3,4,5"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"quadra_1,2,4,5"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"1,2,4,5"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"full"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"1,2,3,4,5"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"random"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"boss_mid"</t>
@@ -270,81 +210,614 @@
   </si>
   <si>
     <t>boss_size</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"boss_random"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"6028","6029","6030"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="20">
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="10"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="11"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F76"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F3F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="0"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFACCCEA"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399980"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -355,26 +828,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
+    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
+    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
+    <cellStyle name="경고문" xfId="9" builtinId="11"/>
+    <cellStyle name="계산" xfId="17" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
+    <cellStyle name="메모" xfId="8" builtinId="10"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="보통" xfId="23" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
+    <cellStyle name="열어본 하이퍼링크" xfId="7" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="20" builtinId="25"/>
+    <cellStyle name="입력" xfId="15" builtinId="20"/>
+    <cellStyle name="제목" xfId="10" builtinId="15"/>
+    <cellStyle name="제목 1" xfId="11" builtinId="16"/>
+    <cellStyle name="제목 2" xfId="12" builtinId="17"/>
+    <cellStyle name="제목 3" xfId="13" builtinId="18"/>
+    <cellStyle name="제목 4" xfId="14" builtinId="19"/>
+    <cellStyle name="좋음" xfId="21" builtinId="26"/>
+    <cellStyle name="출력" xfId="16" builtinId="21"/>
+    <cellStyle name="통화" xfId="2" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="5" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="6" builtinId="8" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -694,17 +1205,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{583B16CD-456E-4C16-9168-F73F26969599}">
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="15.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="1" max="1" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" style="1" width="15.38000011" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="3" style="1" width="20.62999916" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="16383" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="16384" max="16384" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -714,11 +1226,8 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -728,13 +1237,10 @@
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>6001</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>60</v>
@@ -742,13 +1248,10 @@
       <c r="C3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>6002</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>58</v>
@@ -756,13 +1259,10 @@
       <c r="C4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="1">
-        <v>6003</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -770,13 +1270,10 @@
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="1">
-        <v>6004</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
@@ -784,13 +1281,10 @@
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="1">
-        <v>6005</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
@@ -798,13 +1292,10 @@
       <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="1">
-        <v>6006</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
@@ -812,13 +1303,10 @@
       <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="1">
-        <v>6007</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
@@ -826,13 +1314,10 @@
       <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="1">
-        <v>6008</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>16</v>
@@ -840,13 +1325,10 @@
       <c r="C10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="1">
-        <v>6009</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>17</v>
@@ -854,13 +1336,10 @@
       <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="1">
-        <v>6010</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -868,13 +1347,10 @@
       <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="1">
-        <v>6011</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>20</v>
@@ -882,13 +1358,10 @@
       <c r="C13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="1">
-        <v>6012</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>23</v>
@@ -896,13 +1369,10 @@
       <c r="C14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="1">
-        <v>6013</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>24</v>
@@ -910,13 +1380,10 @@
       <c r="C15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="1">
-        <v>6014</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>25</v>
@@ -924,13 +1391,10 @@
       <c r="C16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="1">
-        <v>6015</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>29</v>
@@ -938,13 +1402,10 @@
       <c r="C17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="1">
-        <v>6016</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>31</v>
@@ -952,13 +1413,10 @@
       <c r="C18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="1">
-        <v>6017</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>33</v>
@@ -966,13 +1424,10 @@
       <c r="C19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="1">
-        <v>6018</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>36</v>
@@ -980,13 +1435,10 @@
       <c r="C20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="1">
-        <v>6019</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>38</v>
@@ -994,13 +1446,10 @@
       <c r="C21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="1">
-        <v>6020</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>40</v>
@@ -1008,13 +1457,10 @@
       <c r="C22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="1">
-        <v>6021</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>43</v>
@@ -1022,13 +1468,10 @@
       <c r="C23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="1">
-        <v>6022</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>45</v>
@@ -1036,13 +1479,10 @@
       <c r="C24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="1">
-        <v>6023</v>
+        <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>48</v>
@@ -1050,13 +1490,10 @@
       <c r="C25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="1">
-        <v>6024</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>50</v>
@@ -1064,13 +1501,10 @@
       <c r="C26" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="1">
-        <v>6025</v>
+        <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>56</v>
@@ -1078,13 +1512,10 @@
       <c r="C27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="1">
-        <v>6026</v>
+        <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>54</v>
@@ -1092,13 +1523,10 @@
       <c r="C28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="1">
-        <v>6027</v>
+        <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>52</v>
@@ -1106,13 +1534,10 @@
       <c r="C29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
-        <v>6028</v>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1">
+        <v>28</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>61</v>
@@ -1120,13 +1545,10 @@
       <c r="C30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
-        <v>6029</v>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1">
+        <v>29</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>62</v>
@@ -1134,13 +1556,10 @@
       <c r="C31" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
-        <v>6030</v>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="1">
+        <v>30</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>63</v>
@@ -1148,13 +1567,10 @@
       <c r="C32" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="1">
-        <v>6031</v>
+        <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>65</v>
@@ -1162,12 +1578,10 @@
       <c r="C33" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="1">
-        <v>3</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/Excels/SpawnLaneData.xlsx
+++ b/Assets/Excels/SpawnLaneData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>ID</t>
   </si>
@@ -216,6 +216,18 @@
   </si>
   <si>
     <t>"6028","6029","6030"</t>
+  </si>
+  <si>
+    <t>"2","3","4"</t>
+  </si>
+  <si>
+    <t>3"</t>
+  </si>
+  <si>
+    <t>"boss_Bottom"</t>
+  </si>
+  <si>
+    <t>"Boss_Top"</t>
   </si>
 </sst>
 </file>
@@ -821,7 +833,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -832,6 +844,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1212,8 +1227,7 @@
     <col min="1" max="1" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
     <col min="2" max="2" style="1" width="15.38000011" customWidth="1" outlineLevel="0"/>
     <col min="3" max="3" style="1" width="20.62999916" customWidth="1" outlineLevel="0"/>
-    <col min="4" max="16383" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="16384" max="16384" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="16384" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1543,7 +1557,7 @@
         <v>61</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1551,10 +1565,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1562,22 +1576,16 @@
         <v>30</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="1">
-        <v>31</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
